--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134276743</v>
       </c>
       <c r="B2" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134276649</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>134276743</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,11 +785,11 @@
         <v>134276649</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -891,6 +891,235 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134276934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>511649</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6991174</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på aspar i området</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134276892</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>511648</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6991202</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,123 +1295,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>134276892</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>511648</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6991202</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sundsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1295,6 +1295,123 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134276892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>511648</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991202</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134276743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967346</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963268</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134276649</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134276934</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,8 +1446,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134276892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,128 +1327,6 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134276934</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>134276892</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>511648</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6991202</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sundsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134276892</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1338,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57473-2024 artfynd.xlsx
+++ b/artfynd/A 57473-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>134961714</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>134967346</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>92027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>134963268</v>
       </c>
       <c r="B5" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1327,6 +1327,128 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134276934</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134276892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slåttjärnbäcken, Slåttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>511648</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991202</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134276892</t>
         </is>
       </c>
     </row>
@@ -1338,6 +1460,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
